--- a/youzi/招商深南东/index.xlsx
+++ b/youzi/招商深南东/index.xlsx
@@ -39,37 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB52331"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,31 +117,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,60 +189,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCE2E3E"/>
         <bgColor/>
       </patternFill>
@@ -195,6 +201,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC32938"/>
         <bgColor/>
       </patternFill>
@@ -219,24 +249,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB2222F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -255,19 +279,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,13 +453,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,157 +537,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -465,151 +603,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -627,25 +651,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -657,19 +675,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -688,24 +706,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2314,7 +2314,7 @@
       <c r="C2" t="str">
         <v>601015</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="12" t="str">
         <v>净卖: -308.44万</v>
       </c>
       <c r="E2">
@@ -2329,40 +2329,40 @@
       <c r="H2">
         <v>-0.32</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="3">
         <v>10.51</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="13">
         <v>13.38</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="1">
         <v>7.64</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="4">
         <v>10.19</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="9">
         <v>8.6</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="6">
         <v>6.69</v>
       </c>
       <c r="O2" s="10">
         <v>1.91</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="7">
         <v>-1.91</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="5">
         <v>-0.96</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="8">
         <v>-0.96</v>
       </c>
       <c r="S2" s="11">
         <v>-0.64</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="2">
         <v>23.57</v>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       <c r="C3" t="str">
         <v>301617</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 2288.65万</v>
       </c>
       <c r="E3">
@@ -2391,37 +2391,37 @@
       <c r="H3">
         <v>2.21</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="26">
         <v>6.26</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="17">
         <v>16.21</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="18">
         <v>17.8</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="19">
         <v>30.66</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="14">
         <v>36.79</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="21">
         <v>36.59</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="22">
         <v>44.45</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="15">
         <v>45.34</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="16">
         <v>40.3</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="20">
         <v>32.27</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="23">
         <v>49.92</v>
       </c>
       <c r="T3" s="24">
@@ -2438,7 +2438,7 @@
       <c r="C4" t="str">
         <v>001332</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -1202.20万</v>
       </c>
       <c r="E4">
@@ -2453,25 +2453,25 @@
       <c r="H4">
         <v>-1</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="30">
         <v>-1.69</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="35">
         <v>4.19</v>
       </c>
-      <c r="K4" s="37">
+      <c r="K4" s="31">
         <v>7</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="32">
         <v>7.3</v>
       </c>
       <c r="M4" s="33">
         <v>12.09</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="27">
         <v>13.36</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="37">
         <v>8.95</v>
       </c>
       <c r="P4" s="38">
@@ -2480,13 +2480,13 @@
       <c r="Q4" s="34">
         <v>15.24</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="36">
         <v>26.45</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="28">
         <v>31.23</v>
       </c>
-      <c r="T4" s="35">
+      <c r="T4" s="39">
         <v>22.13</v>
       </c>
     </row>
@@ -2515,40 +2515,40 @@
       <c r="H5">
         <v>-3.79</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="47">
         <v>14.37</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="41">
         <v>18.65</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="48">
         <v>17.11</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="49">
         <v>11.3</v>
       </c>
       <c r="M5" s="42">
         <v>9.76</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="50">
         <v>4.61</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="45">
         <v>3.68</v>
       </c>
       <c r="P5" s="43">
         <v>2.41</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="46">
         <v>-1.4</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="51">
         <v>-4.81</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="44">
         <v>-2.27</v>
       </c>
-      <c r="T5" s="49">
+      <c r="T5" s="52">
         <v>-8.56</v>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       <c r="C6" t="str">
         <v>002716</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="62" t="str">
         <v>净买: 1382.25万</v>
       </c>
       <c r="E6">
@@ -2577,40 +2577,40 @@
       <c r="H6">
         <v>-10</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="65">
         <v>2.54</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="54">
         <v>4.29</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="55">
         <v>1.59</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="56">
         <v>2.22</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="60">
         <v>-0.79</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="57">
         <v>2.86</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="63">
         <v>1.11</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="64">
         <v>2.06</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="58">
         <v>0.79</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="53">
         <v>-2.7</v>
       </c>
-      <c r="S6" s="65">
+      <c r="S6" s="59">
         <v>-2.22</v>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="61">
         <v>91.75</v>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       <c r="C7" t="str">
         <v>600179</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="68" t="str">
         <v>净卖: -4985.00万</v>
       </c>
       <c r="E7">
@@ -2639,40 +2639,40 @@
       <c r="H7">
         <v>10.07</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="76">
         <v>0</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="73">
         <v>9.96</v>
       </c>
       <c r="K7" s="75">
         <v>20.93</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="69">
         <v>33.13</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="77">
         <v>19.92</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="78">
         <v>11.59</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="70">
         <v>12.2</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="74">
         <v>5.69</v>
       </c>
       <c r="Q7" s="66">
         <v>6.3</v>
       </c>
-      <c r="R7" s="74">
+      <c r="R7" s="71">
         <v>6.3</v>
       </c>
       <c r="S7" s="67">
         <v>4.07</v>
       </c>
-      <c r="T7" s="70">
+      <c r="T7" s="72">
         <v>-9.15</v>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       <c r="C8" t="str">
         <v>603138</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="81" t="str">
         <v>净卖: -1937.66万</v>
       </c>
       <c r="E8">
@@ -2701,40 +2701,40 @@
       <c r="H8">
         <v>10.02</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="85">
         <v>0</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="82">
         <v>2.79</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="86">
         <v>-7.47</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="89">
         <v>-1.28</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="91">
         <v>-1.59</v>
       </c>
-      <c r="N8" s="81">
+      <c r="N8" s="90">
         <v>0.8</v>
       </c>
-      <c r="O8" s="88">
+      <c r="O8" s="83">
         <v>-1.41</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="79">
         <v>-8.58</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="87">
         <v>-10.21</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="88">
         <v>-6.28</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="80">
         <v>-6.41</v>
       </c>
-      <c r="T8" s="90">
+      <c r="T8" s="84">
         <v>-7.6</v>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       <c r="C9" t="str">
         <v>605162</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="94" t="str">
         <v>净卖: -614.82万</v>
       </c>
       <c r="E9">
@@ -2763,13 +2763,13 @@
       <c r="H9">
         <v>-5.12</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="95">
         <v>-3.83</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="96">
         <v>-2.18</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="92">
         <v>-4.43</v>
       </c>
       <c r="L9" t="str"/>
@@ -2780,7 +2780,7 @@
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="95">
+      <c r="T9" s="93">
         <v>-4.43</v>
       </c>
     </row>
@@ -2843,40 +2843,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="99">
+      <c r="I11" s="98">
         <v>50</v>
       </c>
       <c r="J11" s="107">
         <v>87.5</v>
       </c>
-      <c r="K11" s="100">
+      <c r="K11" s="103">
         <v>75</v>
       </c>
-      <c r="L11" s="108">
+      <c r="L11" s="99">
         <v>85.71</v>
       </c>
-      <c r="M11" s="97">
+      <c r="M11" s="108">
         <v>71.43</v>
       </c>
-      <c r="N11" s="101">
+      <c r="N11" s="100">
         <v>100</v>
       </c>
-      <c r="O11" s="102">
+      <c r="O11" s="104">
         <v>85.71</v>
       </c>
-      <c r="P11" s="105">
+      <c r="P11" s="101">
         <v>71.43</v>
       </c>
-      <c r="Q11" s="106">
+      <c r="Q11" s="105">
         <v>57.14</v>
       </c>
-      <c r="R11" s="98">
+      <c r="R11" s="106">
         <v>42.86</v>
       </c>
-      <c r="S11" s="103">
+      <c r="S11" s="102">
         <v>42.86</v>
       </c>
-      <c r="T11" s="104">
+      <c r="T11" s="97">
         <v>50</v>
       </c>
     </row>
@@ -2891,40 +2891,40 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="109">
+      <c r="I12" s="112">
         <v>3.52</v>
       </c>
-      <c r="J12" s="110">
+      <c r="J12" s="116">
         <v>8.41</v>
       </c>
-      <c r="K12" s="117">
+      <c r="K12" s="109">
         <v>7.52</v>
       </c>
       <c r="L12" s="113">
         <v>13.36</v>
       </c>
-      <c r="M12" s="120">
+      <c r="M12" s="114">
         <v>12.11</v>
       </c>
-      <c r="N12" s="111">
+      <c r="N12" s="117">
         <v>10.93</v>
       </c>
-      <c r="O12" s="118">
+      <c r="O12" s="111">
         <v>10.13</v>
       </c>
-      <c r="P12" s="114">
+      <c r="P12" s="110">
         <v>8.54</v>
       </c>
-      <c r="Q12" s="112">
+      <c r="Q12" s="115">
         <v>7.15</v>
       </c>
-      <c r="R12" s="115">
+      <c r="R12" s="118">
         <v>7.18</v>
       </c>
-      <c r="S12" s="116">
+      <c r="S12" s="119">
         <v>10.53</v>
       </c>
-      <c r="T12" s="119">
+      <c r="T12" s="120">
         <v>17.7</v>
       </c>
     </row>

--- a/youzi/招商深南东/index.xlsx
+++ b/youzi/招商深南东/index.xlsx
@@ -39,67 +39,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC02836"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCA2C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF1B1B7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,73 +249,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,19 +393,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,61 +507,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,163 +585,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,48 +615,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -501,43 +627,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
+        <fgColor rgb="FFE66E7A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -549,96 +639,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -663,7 +663,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -699,19 +711,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2314,7 +2314,7 @@
       <c r="C2" t="str">
         <v>601015</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -308.44万</v>
       </c>
       <c r="E2">
@@ -2329,40 +2329,40 @@
       <c r="H2">
         <v>-0.32</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>10.51</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="7">
         <v>13.38</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="11">
         <v>7.64</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="8">
         <v>10.19</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="5">
         <v>8.6</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="12">
         <v>6.69</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="13">
         <v>1.91</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="9">
         <v>-1.91</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="1">
         <v>-0.96</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="10">
         <v>-0.96</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="3">
         <v>-0.64</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="6">
         <v>23.57</v>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       <c r="C3" t="str">
         <v>301617</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 2288.65万</v>
       </c>
       <c r="E3">
@@ -2391,40 +2391,40 @@
       <c r="H3">
         <v>2.21</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="14">
         <v>6.26</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="15">
         <v>16.21</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="16">
         <v>17.8</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="18">
         <v>30.66</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="19">
         <v>36.79</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="23">
         <v>36.59</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="20">
         <v>44.45</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="24">
         <v>45.34</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="21">
         <v>40.3</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="25">
         <v>32.27</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="22">
         <v>49.92</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="17">
         <v>33.91</v>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       <c r="C4" t="str">
         <v>001332</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -1202.20万</v>
       </c>
       <c r="E4">
@@ -2453,40 +2453,40 @@
       <c r="H4">
         <v>-1</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="36">
         <v>-1.69</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="30">
         <v>4.19</v>
       </c>
       <c r="K4" s="31">
         <v>7</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="37">
         <v>7.3</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="38">
         <v>12.09</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="34">
         <v>13.36</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="32">
         <v>8.95</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="27">
         <v>14.78</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="33">
         <v>15.24</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="28">
         <v>26.45</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="39">
         <v>31.23</v>
       </c>
-      <c r="T4" s="39">
+      <c r="T4" s="29">
         <v>22.13</v>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       <c r="C5" t="str">
         <v>002674</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="44" t="str">
         <v>净卖: -488.16万</v>
       </c>
       <c r="E5">
@@ -2515,37 +2515,37 @@
       <c r="H5">
         <v>-3.79</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="40">
         <v>14.37</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="45">
         <v>18.65</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="41">
         <v>17.11</v>
       </c>
       <c r="L5" s="49">
         <v>11.3</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="50">
         <v>9.76</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="42">
         <v>4.61</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="43">
         <v>3.68</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="51">
         <v>2.41</v>
       </c>
       <c r="Q5" s="46">
         <v>-1.4</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="47">
         <v>-4.81</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="48">
         <v>-2.27</v>
       </c>
       <c r="T5" s="52">
@@ -2562,7 +2562,7 @@
       <c r="C6" t="str">
         <v>002716</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="59" t="str">
         <v>净买: 1382.25万</v>
       </c>
       <c r="E6">
@@ -2577,40 +2577,40 @@
       <c r="H6">
         <v>-10</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="53">
         <v>2.54</v>
       </c>
       <c r="J6" s="54">
         <v>4.29</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="60">
         <v>1.59</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="55">
         <v>2.22</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="56">
         <v>-0.79</v>
       </c>
       <c r="N6" s="57">
         <v>2.86</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="62">
         <v>1.11</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="58">
         <v>2.06</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="63">
         <v>0.79</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="64">
         <v>-2.7</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="61">
         <v>-2.22</v>
       </c>
-      <c r="T6" s="61">
+      <c r="T6" s="65">
         <v>91.75</v>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       <c r="C7" t="str">
         <v>600179</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="78" t="str">
         <v>净卖: -4985.00万</v>
       </c>
       <c r="E7">
@@ -2639,40 +2639,40 @@
       <c r="H7">
         <v>10.07</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="68">
         <v>0</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="75">
         <v>9.96</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="76">
         <v>20.93</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="71">
         <v>33.13</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="69">
         <v>19.92</v>
       </c>
-      <c r="N7" s="78">
+      <c r="N7" s="70">
         <v>11.59</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="72">
         <v>12.2</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="66">
         <v>5.69</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="67">
         <v>6.3</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="77">
         <v>6.3</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="73">
         <v>4.07</v>
       </c>
-      <c r="T7" s="72">
+      <c r="T7" s="74">
         <v>-9.15</v>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       <c r="C8" t="str">
         <v>603138</v>
       </c>
-      <c r="D8" s="81" t="str">
+      <c r="D8" s="91" t="str">
         <v>净卖: -1937.66万</v>
       </c>
       <c r="E8">
@@ -2701,40 +2701,40 @@
       <c r="H8">
         <v>10.02</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="79">
         <v>0</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="80">
         <v>2.79</v>
       </c>
-      <c r="K8" s="86">
+      <c r="K8" s="87">
         <v>-7.47</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="88">
         <v>-1.28</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="84">
         <v>-1.59</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="89">
         <v>0.8</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="81">
         <v>-1.41</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="82">
         <v>-8.58</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="85">
         <v>-10.21</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="83">
         <v>-6.28</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="90">
         <v>-6.41</v>
       </c>
-      <c r="T8" s="84">
+      <c r="T8" s="86">
         <v>-7.6</v>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       <c r="C9" t="str">
         <v>605162</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -614.82万</v>
       </c>
       <c r="E9">
@@ -2763,13 +2763,13 @@
       <c r="H9">
         <v>-5.12</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="92">
         <v>-3.83</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="93">
         <v>-2.18</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="94">
         <v>-4.43</v>
       </c>
       <c r="L9" t="str"/>
@@ -2780,7 +2780,7 @@
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="93">
+      <c r="T9" s="95">
         <v>-4.43</v>
       </c>
     </row>
@@ -2843,37 +2843,37 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="98">
+      <c r="I11" s="100">
         <v>50</v>
       </c>
-      <c r="J11" s="107">
+      <c r="J11" s="103">
         <v>87.5</v>
       </c>
-      <c r="K11" s="103">
+      <c r="K11" s="104">
         <v>75</v>
       </c>
-      <c r="L11" s="99">
+      <c r="L11" s="98">
         <v>85.71</v>
       </c>
-      <c r="M11" s="108">
+      <c r="M11" s="101">
         <v>71.43</v>
       </c>
-      <c r="N11" s="100">
+      <c r="N11" s="105">
         <v>100</v>
       </c>
-      <c r="O11" s="104">
+      <c r="O11" s="106">
         <v>85.71</v>
       </c>
-      <c r="P11" s="101">
+      <c r="P11" s="107">
         <v>71.43</v>
       </c>
-      <c r="Q11" s="105">
+      <c r="Q11" s="99">
         <v>57.14</v>
       </c>
-      <c r="R11" s="106">
+      <c r="R11" s="102">
         <v>42.86</v>
       </c>
-      <c r="S11" s="102">
+      <c r="S11" s="108">
         <v>42.86</v>
       </c>
       <c r="T11" s="97">
@@ -2891,37 +2891,37 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="112">
+      <c r="I12" s="113">
         <v>3.52</v>
       </c>
-      <c r="J12" s="116">
+      <c r="J12" s="118">
         <v>8.41</v>
       </c>
-      <c r="K12" s="109">
+      <c r="K12" s="114">
         <v>7.52</v>
       </c>
-      <c r="L12" s="113">
+      <c r="L12" s="109">
         <v>13.36</v>
       </c>
-      <c r="M12" s="114">
+      <c r="M12" s="119">
         <v>12.11</v>
       </c>
-      <c r="N12" s="117">
+      <c r="N12" s="115">
         <v>10.93</v>
       </c>
-      <c r="O12" s="111">
+      <c r="O12" s="116">
         <v>10.13</v>
       </c>
-      <c r="P12" s="110">
+      <c r="P12" s="117">
         <v>8.54</v>
       </c>
-      <c r="Q12" s="115">
+      <c r="Q12" s="110">
         <v>7.15</v>
       </c>
-      <c r="R12" s="118">
+      <c r="R12" s="111">
         <v>7.18</v>
       </c>
-      <c r="S12" s="119">
+      <c r="S12" s="112">
         <v>10.53</v>
       </c>
       <c r="T12" s="120">

--- a/youzi/招商深南东/index.xlsx
+++ b/youzi/招商深南东/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="122">
+  <fills count="123">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,145 +39,349 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD5EEDB"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE3F3E7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,37 +399,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -249,49 +507,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,139 +585,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -459,186 +675,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE66E7A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -663,54 +705,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB32230"/>
         <bgColor/>
       </patternFill>
@@ -757,8 +751,27 @@
         <bgColor/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="121">
+  <borders count="122">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1610,7 +1623,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1970,6 +1983,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="120" fillId="121" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="121" fillId="122" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -2314,7 +2330,7 @@
       <c r="C2" t="str">
         <v>601015</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -308.44万</v>
       </c>
       <c r="E2">
@@ -2329,41 +2345,41 @@
       <c r="H2">
         <v>-0.32</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="11">
         <v>10.51</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="12">
         <v>13.38</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="7">
         <v>7.64</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="13">
         <v>10.19</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="8">
         <v>8.6</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="4">
         <v>6.69</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="1">
         <v>1.91</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="2">
         <v>-1.91</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="5">
         <v>-0.96</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="9">
         <v>-0.96</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="6">
         <v>-0.64</v>
       </c>
-      <c r="T2" s="6">
-        <v>23.57</v>
+      <c r="T2" s="10">
+        <v>25.48</v>
       </c>
     </row>
     <row r="3">
@@ -2376,7 +2392,7 @@
       <c r="C3" t="str">
         <v>301617</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="16" t="str">
         <v>净买: 2288.65万</v>
       </c>
       <c r="E3">
@@ -2391,41 +2407,41 @@
       <c r="H3">
         <v>2.21</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="24">
         <v>6.26</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="17">
         <v>16.21</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="18">
         <v>17.8</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="19">
         <v>30.66</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="25">
         <v>36.79</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="21">
         <v>36.59</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="26">
         <v>44.45</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="20">
         <v>45.34</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="14">
         <v>40.3</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="22">
         <v>32.27</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="23">
         <v>49.92</v>
       </c>
-      <c r="T3" s="17">
-        <v>33.91</v>
+      <c r="T3" s="15">
+        <v>31.09</v>
       </c>
     </row>
     <row r="4">
@@ -2438,7 +2454,7 @@
       <c r="C4" t="str">
         <v>001332</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="28" t="str">
         <v>净卖: -1202.20万</v>
       </c>
       <c r="E4">
@@ -2453,41 +2469,41 @@
       <c r="H4">
         <v>-1</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="34">
         <v>-1.69</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="35">
         <v>4.19</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="29">
         <v>7</v>
       </c>
-      <c r="L4" s="37">
+      <c r="L4" s="30">
         <v>7.3</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="31">
         <v>12.09</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="36">
         <v>13.36</v>
       </c>
       <c r="O4" s="32">
         <v>8.95</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="37">
         <v>14.78</v>
       </c>
       <c r="Q4" s="33">
         <v>15.24</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="38">
         <v>26.45</v>
       </c>
       <c r="S4" s="39">
         <v>31.23</v>
       </c>
-      <c r="T4" s="29">
-        <v>22.13</v>
+      <c r="T4" s="27">
+        <v>26.96</v>
       </c>
     </row>
     <row r="5">
@@ -2500,7 +2516,7 @@
       <c r="C5" t="str">
         <v>002674</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -488.16万</v>
       </c>
       <c r="E5">
@@ -2515,41 +2531,41 @@
       <c r="H5">
         <v>-3.79</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="42">
         <v>14.37</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="52">
         <v>18.65</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="43">
         <v>17.11</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="40">
         <v>11.3</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="46">
         <v>9.76</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="47">
         <v>4.61</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="44">
         <v>3.68</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="41">
         <v>2.41</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="50">
         <v>-1.4</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="48">
         <v>-4.81</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="49">
         <v>-2.27</v>
       </c>
-      <c r="T5" s="52">
-        <v>-8.56</v>
+      <c r="T5" s="51">
+        <v>-7.09</v>
       </c>
     </row>
     <row r="6">
@@ -2562,7 +2578,7 @@
       <c r="C6" t="str">
         <v>002716</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="60" t="str">
         <v>净买: 1382.25万</v>
       </c>
       <c r="E6">
@@ -2577,41 +2593,41 @@
       <c r="H6">
         <v>-10</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="65">
         <v>2.54</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="57">
         <v>4.29</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="61">
         <v>1.59</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="62">
         <v>2.22</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="53">
         <v>-0.79</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="63">
         <v>2.86</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="54">
         <v>1.11</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="55">
         <v>2.06</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="56">
         <v>0.79</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="58">
         <v>-2.7</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="64">
         <v>-2.22</v>
       </c>
-      <c r="T6" s="65">
-        <v>91.75</v>
+      <c r="T6" s="59">
+        <v>95.56</v>
       </c>
     </row>
     <row r="7">
@@ -2639,41 +2655,41 @@
       <c r="H7">
         <v>10.07</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="66">
         <v>0</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="76">
         <v>9.96</v>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="72">
         <v>20.93</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="77">
         <v>33.13</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="73">
         <v>19.92</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="67">
         <v>11.59</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="74">
         <v>12.2</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="68">
         <v>5.69</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="69">
         <v>6.3</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="75">
         <v>6.3</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="70">
         <v>4.07</v>
       </c>
-      <c r="T7" s="74">
-        <v>-9.15</v>
+      <c r="T7" s="71">
+        <v>-8.13</v>
       </c>
     </row>
     <row r="8">
@@ -2701,19 +2717,19 @@
       <c r="H8">
         <v>10.02</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="87">
         <v>0</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="88">
         <v>2.79</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="84">
         <v>-7.47</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="79">
         <v>-1.28</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="80">
         <v>-1.59</v>
       </c>
       <c r="N8" s="89">
@@ -2725,17 +2741,17 @@
       <c r="P8" s="82">
         <v>-8.58</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="83">
         <v>-10.21</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8" s="85">
         <v>-6.28</v>
       </c>
       <c r="S8" s="90">
         <v>-6.41</v>
       </c>
       <c r="T8" s="86">
-        <v>-7.6</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="9">
@@ -2748,7 +2764,7 @@
       <c r="C9" t="str">
         <v>605162</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="95" t="str">
         <v>净卖: -614.82万</v>
       </c>
       <c r="E9">
@@ -2763,16 +2779,18 @@
       <c r="H9">
         <v>-5.12</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="96">
         <v>-3.83</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="97">
         <v>-2.18</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="92">
         <v>-4.43</v>
       </c>
-      <c r="L9" t="str"/>
+      <c r="L9" s="93">
+        <v>5.1</v>
+      </c>
       <c r="M9" t="str"/>
       <c r="N9" t="str"/>
       <c r="O9" t="str"/>
@@ -2780,8 +2798,8 @@
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="95">
-        <v>-4.43</v>
+      <c r="T9" s="94">
+        <v>5.1</v>
       </c>
     </row>
     <row r="10">
@@ -2805,7 +2823,7 @@
         <v>8</v>
       </c>
       <c r="L10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M10">
         <v>7</v>
@@ -2843,41 +2861,41 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="100">
+      <c r="I11" s="104">
         <v>50</v>
       </c>
-      <c r="J11" s="103">
+      <c r="J11" s="98">
         <v>87.5</v>
       </c>
-      <c r="K11" s="104">
+      <c r="K11" s="108">
         <v>75</v>
       </c>
-      <c r="L11" s="98">
+      <c r="L11" s="99">
+        <v>87.5</v>
+      </c>
+      <c r="M11" s="100">
+        <v>71.43</v>
+      </c>
+      <c r="N11" s="102">
+        <v>100</v>
+      </c>
+      <c r="O11" s="105">
         <v>85.71</v>
       </c>
-      <c r="M11" s="101">
+      <c r="P11" s="106">
         <v>71.43</v>
       </c>
-      <c r="N11" s="105">
-        <v>100</v>
-      </c>
-      <c r="O11" s="106">
-        <v>85.71</v>
-      </c>
-      <c r="P11" s="107">
-        <v>71.43</v>
-      </c>
-      <c r="Q11" s="99">
+      <c r="Q11" s="107">
         <v>57.14</v>
       </c>
-      <c r="R11" s="102">
+      <c r="R11" s="103">
         <v>42.86</v>
       </c>
-      <c r="S11" s="108">
+      <c r="S11" s="109">
         <v>42.86</v>
       </c>
-      <c r="T11" s="97">
-        <v>50</v>
+      <c r="T11" s="101">
+        <v>62.5</v>
       </c>
     </row>
     <row r="12">
@@ -2891,41 +2909,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="113">
+      <c r="I12" s="112">
         <v>3.52</v>
       </c>
-      <c r="J12" s="118">
+      <c r="J12" s="116">
         <v>8.41</v>
       </c>
-      <c r="K12" s="114">
+      <c r="K12" s="117">
         <v>7.52</v>
       </c>
-      <c r="L12" s="109">
-        <v>13.36</v>
-      </c>
-      <c r="M12" s="119">
+      <c r="L12" s="118">
+        <v>12.33</v>
+      </c>
+      <c r="M12" s="113">
         <v>12.11</v>
       </c>
-      <c r="N12" s="115">
+      <c r="N12" s="119">
         <v>10.93</v>
       </c>
-      <c r="O12" s="116">
+      <c r="O12" s="114">
         <v>10.13</v>
       </c>
-      <c r="P12" s="117">
+      <c r="P12" s="120">
         <v>8.54</v>
       </c>
-      <c r="Q12" s="110">
+      <c r="Q12" s="115">
         <v>7.15</v>
       </c>
-      <c r="R12" s="111">
+      <c r="R12" s="121">
         <v>7.18</v>
       </c>
-      <c r="S12" s="112">
+      <c r="S12" s="110">
         <v>10.53</v>
       </c>
-      <c r="T12" s="120">
-        <v>17.7</v>
+      <c r="T12" s="111">
+        <v>20.18</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/招商深南东/index.xlsx
+++ b/youzi/招商深南东/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="123">
+  <fills count="124">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,13 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF1B1B7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
+        <fgColor rgb="FFE3F3E7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,48 +105,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -171,12 +177,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCE2E3E"/>
         <bgColor/>
       </patternFill>
@@ -201,19 +201,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
+        <fgColor rgb="FFB6E1C0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,49 +273,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF218F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,7 +339,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,25 +483,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,91 +525,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
+        <fgColor rgb="FF1D7C34"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -435,67 +537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -507,49 +549,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC7E8CF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF24973F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -561,61 +645,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -651,54 +693,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -763,8 +757,27 @@
         <bgColor/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="122">
+  <borders count="123">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1623,7 +1636,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1986,6 +1999,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="121" fillId="122" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="122" fillId="123" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -2330,7 +2346,7 @@
       <c r="C2" t="str">
         <v>601015</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -308.44万</v>
       </c>
       <c r="E2">
@@ -2345,41 +2361,41 @@
       <c r="H2">
         <v>-0.32</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="13">
         <v>10.51</v>
       </c>
       <c r="J2" s="12">
         <v>13.38</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="4">
         <v>7.64</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="5">
         <v>10.19</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="1">
         <v>8.6</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="6">
         <v>6.69</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="9">
         <v>1.91</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="7">
         <v>-1.91</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="2">
         <v>-0.96</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="3">
         <v>-0.96</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="10">
         <v>-0.64</v>
       </c>
-      <c r="T2" s="10">
-        <v>25.48</v>
+      <c r="T2" s="8">
+        <v>27.39</v>
       </c>
     </row>
     <row r="3">
@@ -2392,7 +2408,7 @@
       <c r="C3" t="str">
         <v>301617</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="17" t="str">
         <v>净买: 2288.65万</v>
       </c>
       <c r="E3">
@@ -2410,38 +2426,38 @@
       <c r="I3" s="24">
         <v>6.26</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="16">
         <v>16.21</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="21">
         <v>17.8</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="22">
         <v>30.66</v>
       </c>
       <c r="M3" s="25">
         <v>36.79</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="18">
         <v>36.59</v>
       </c>
       <c r="O3" s="26">
         <v>44.45</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="19">
         <v>45.34</v>
       </c>
       <c r="Q3" s="14">
         <v>40.3</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="15">
         <v>32.27</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="20">
         <v>49.92</v>
       </c>
-      <c r="T3" s="15">
-        <v>31.09</v>
+      <c r="T3" s="23">
+        <v>32.69</v>
       </c>
     </row>
     <row r="4">
@@ -2454,7 +2470,7 @@
       <c r="C4" t="str">
         <v>001332</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="36" t="str">
         <v>净卖: -1202.20万</v>
       </c>
       <c r="E4">
@@ -2469,41 +2485,41 @@
       <c r="H4">
         <v>-1</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="37">
         <v>-1.69</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="34">
         <v>4.19</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="30">
         <v>7</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="31">
         <v>7.3</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="35">
         <v>12.09</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="38">
         <v>13.36</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="39">
         <v>8.95</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="27">
         <v>14.78</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="32">
         <v>15.24</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="33">
         <v>26.45</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="28">
         <v>31.23</v>
       </c>
-      <c r="T4" s="27">
-        <v>26.96</v>
+      <c r="T4" s="29">
+        <v>26.41</v>
       </c>
     </row>
     <row r="5">
@@ -2516,7 +2532,7 @@
       <c r="C5" t="str">
         <v>002674</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="42" t="str">
         <v>净卖: -488.16万</v>
       </c>
       <c r="E5">
@@ -2531,41 +2547,41 @@
       <c r="H5">
         <v>-3.79</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="49">
         <v>14.37</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="43">
         <v>18.65</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="50">
         <v>17.11</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="51">
         <v>11.3</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="44">
         <v>9.76</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="46">
         <v>4.61</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="47">
         <v>3.68</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="48">
         <v>2.41</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="52">
         <v>-1.4</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="45">
         <v>-4.81</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="41">
         <v>-2.27</v>
       </c>
-      <c r="T5" s="51">
-        <v>-7.09</v>
+      <c r="T5" s="40">
+        <v>-7.02</v>
       </c>
     </row>
     <row r="6">
@@ -2578,7 +2594,7 @@
       <c r="C6" t="str">
         <v>002716</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="58" t="str">
         <v>净买: 1382.25万</v>
       </c>
       <c r="E6">
@@ -2593,41 +2609,41 @@
       <c r="H6">
         <v>-10</v>
       </c>
-      <c r="I6" s="65">
+      <c r="I6" s="64">
         <v>2.54</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="62">
         <v>4.29</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="65">
         <v>1.59</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="53">
         <v>2.22</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="55">
         <v>-0.79</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="56">
         <v>2.86</v>
       </c>
       <c r="O6" s="54">
         <v>1.11</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="59">
         <v>2.06</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="60">
         <v>0.79</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="57">
         <v>-2.7</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="63">
         <v>-2.22</v>
       </c>
-      <c r="T6" s="59">
-        <v>95.56</v>
+      <c r="T6" s="61">
+        <v>95.87</v>
       </c>
     </row>
     <row r="7">
@@ -2640,7 +2656,7 @@
       <c r="C7" t="str">
         <v>600179</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -4985.00万</v>
       </c>
       <c r="E7">
@@ -2655,41 +2671,41 @@
       <c r="H7">
         <v>10.07</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="77">
         <v>0</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="66">
         <v>9.96</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="67">
         <v>20.93</v>
       </c>
-      <c r="L7" s="77">
+      <c r="L7" s="70">
         <v>33.13</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="71">
         <v>19.92</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="68">
         <v>11.59</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="75">
         <v>12.2</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="72">
         <v>5.69</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="76">
         <v>6.3</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="73">
         <v>6.3</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="69">
         <v>4.07</v>
       </c>
-      <c r="T7" s="71">
-        <v>-8.13</v>
+      <c r="T7" s="78">
+        <v>-7.72</v>
       </c>
     </row>
     <row r="8">
@@ -2702,7 +2718,7 @@
       <c r="C8" t="str">
         <v>603138</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="85" t="str">
         <v>净卖: -1937.66万</v>
       </c>
       <c r="E8">
@@ -2717,22 +2733,22 @@
       <c r="H8">
         <v>10.02</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="83">
         <v>0</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="79">
         <v>2.79</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="89">
         <v>-7.47</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="90">
         <v>-1.28</v>
       </c>
       <c r="M8" s="80">
         <v>-1.59</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="86">
         <v>0.8</v>
       </c>
       <c r="O8" s="81">
@@ -2741,17 +2757,17 @@
       <c r="P8" s="82">
         <v>-8.58</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="84">
         <v>-10.21</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="91">
         <v>-6.28</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="87">
         <v>-6.41</v>
       </c>
-      <c r="T8" s="86">
-        <v>-7.56</v>
+      <c r="T8" s="88">
+        <v>-13.35</v>
       </c>
     </row>
     <row r="9">
@@ -2764,7 +2780,7 @@
       <c r="C9" t="str">
         <v>605162</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="98" t="str">
         <v>净卖: -614.82万</v>
       </c>
       <c r="E9">
@@ -2779,27 +2795,29 @@
       <c r="H9">
         <v>-5.12</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="92">
         <v>-3.83</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="93">
         <v>-2.18</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="94">
         <v>-4.43</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="95">
         <v>5.1</v>
       </c>
-      <c r="M9" t="str"/>
+      <c r="M9" s="96">
+        <v>3.98</v>
+      </c>
       <c r="N9" t="str"/>
       <c r="O9" t="str"/>
       <c r="P9" t="str"/>
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="94">
-        <v>5.1</v>
+      <c r="T9" s="97">
+        <v>3.98</v>
       </c>
     </row>
     <row r="10">
@@ -2826,7 +2844,7 @@
         <v>8</v>
       </c>
       <c r="M10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>7</v>
@@ -2861,40 +2879,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="104">
+      <c r="I11" s="101">
         <v>50</v>
       </c>
-      <c r="J11" s="98">
+      <c r="J11" s="107">
         <v>87.5</v>
       </c>
-      <c r="K11" s="108">
+      <c r="K11" s="104">
         <v>75</v>
       </c>
-      <c r="L11" s="99">
+      <c r="L11" s="109">
         <v>87.5</v>
       </c>
-      <c r="M11" s="100">
+      <c r="M11" s="105">
+        <v>75</v>
+      </c>
+      <c r="N11" s="106">
+        <v>100</v>
+      </c>
+      <c r="O11" s="110">
+        <v>85.71</v>
+      </c>
+      <c r="P11" s="99">
         <v>71.43</v>
       </c>
-      <c r="N11" s="102">
-        <v>100</v>
-      </c>
-      <c r="O11" s="105">
-        <v>85.71</v>
-      </c>
-      <c r="P11" s="106">
-        <v>71.43</v>
-      </c>
-      <c r="Q11" s="107">
+      <c r="Q11" s="100">
         <v>57.14</v>
       </c>
-      <c r="R11" s="103">
+      <c r="R11" s="102">
         <v>42.86</v>
       </c>
-      <c r="S11" s="109">
+      <c r="S11" s="103">
         <v>42.86</v>
       </c>
-      <c r="T11" s="101">
+      <c r="T11" s="108">
         <v>62.5</v>
       </c>
     </row>
@@ -2909,7 +2927,7 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="112">
+      <c r="I12" s="111">
         <v>3.52</v>
       </c>
       <c r="J12" s="116">
@@ -2918,32 +2936,32 @@
       <c r="K12" s="117">
         <v>7.52</v>
       </c>
-      <c r="L12" s="118">
+      <c r="L12" s="121">
         <v>12.33</v>
       </c>
-      <c r="M12" s="113">
-        <v>12.11</v>
-      </c>
-      <c r="N12" s="119">
+      <c r="M12" s="112">
+        <v>11.1</v>
+      </c>
+      <c r="N12" s="114">
         <v>10.93</v>
       </c>
-      <c r="O12" s="114">
+      <c r="O12" s="118">
         <v>10.13</v>
       </c>
-      <c r="P12" s="120">
+      <c r="P12" s="115">
         <v>8.54</v>
       </c>
-      <c r="Q12" s="115">
+      <c r="Q12" s="113">
         <v>7.15</v>
       </c>
-      <c r="R12" s="121">
+      <c r="R12" s="119">
         <v>7.18</v>
       </c>
-      <c r="S12" s="110">
+      <c r="S12" s="120">
         <v>10.53</v>
       </c>
-      <c r="T12" s="111">
-        <v>20.18</v>
+      <c r="T12" s="122">
+        <v>19.78</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/招商深南东/index.xlsx
+++ b/youzi/招商深南东/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="124">
+  <fills count="127">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,97 +39,313 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB52331"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD5EEDB"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD5EEDB"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE3F3E7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,109 +357,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -255,31 +495,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -291,187 +561,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -483,13 +597,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -501,132 +687,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -639,49 +705,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -745,32 +787,29 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="123">
+  <borders count="126">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1636,7 +1675,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="126">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -2002,6 +2041,15 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="122" fillId="123" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="123" fillId="124" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="124" fillId="125" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="125" fillId="126" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -2346,7 +2394,7 @@
       <c r="C2" t="str">
         <v>601015</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="7" t="str">
         <v>净卖: -308.44万</v>
       </c>
       <c r="E2">
@@ -2361,41 +2409,41 @@
       <c r="H2">
         <v>-0.32</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="1">
         <v>10.51</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="8">
         <v>13.38</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="5">
         <v>7.64</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="6">
         <v>10.19</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <v>8.6</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="3">
         <v>6.69</v>
       </c>
       <c r="O2" s="9">
         <v>1.91</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="10">
         <v>-1.91</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="4">
         <v>-0.96</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="11">
         <v>-0.96</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="12">
         <v>-0.64</v>
       </c>
-      <c r="T2" s="8">
-        <v>27.39</v>
+      <c r="T2" s="13">
+        <v>26.75</v>
       </c>
     </row>
     <row r="3">
@@ -2408,7 +2456,7 @@
       <c r="C3" t="str">
         <v>301617</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="16" t="str">
         <v>净买: 2288.65万</v>
       </c>
       <c r="E3">
@@ -2423,41 +2471,41 @@
       <c r="H3">
         <v>2.21</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="18">
         <v>6.26</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="17">
         <v>16.21</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="24">
         <v>17.8</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="20">
         <v>30.66</v>
       </c>
       <c r="M3" s="25">
         <v>36.79</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="19">
         <v>36.59</v>
       </c>
       <c r="O3" s="26">
         <v>44.45</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="21">
         <v>45.34</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="22">
         <v>40.3</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="14">
         <v>32.27</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="15">
         <v>49.92</v>
       </c>
       <c r="T3" s="23">
-        <v>32.69</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="4">
@@ -2485,19 +2533,19 @@
       <c r="H4">
         <v>-1</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="33">
         <v>-1.69</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="37">
         <v>4.19</v>
       </c>
       <c r="K4" s="30">
         <v>7</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="28">
         <v>7.3</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="29">
         <v>12.09</v>
       </c>
       <c r="N4" s="38">
@@ -2506,20 +2554,20 @@
       <c r="O4" s="39">
         <v>8.95</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="31">
         <v>14.78</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="27">
         <v>15.24</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="32">
         <v>26.45</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="34">
         <v>31.23</v>
       </c>
-      <c r="T4" s="29">
-        <v>26.41</v>
+      <c r="T4" s="35">
+        <v>25.29</v>
       </c>
     </row>
     <row r="5">
@@ -2532,7 +2580,7 @@
       <c r="C5" t="str">
         <v>002674</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -488.16万</v>
       </c>
       <c r="E5">
@@ -2547,10 +2595,10 @@
       <c r="H5">
         <v>-3.79</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="47">
         <v>14.37</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="49">
         <v>18.65</v>
       </c>
       <c r="K5" s="50">
@@ -2559,29 +2607,29 @@
       <c r="L5" s="51">
         <v>11.3</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="45">
         <v>9.76</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="42">
         <v>4.61</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="48">
         <v>3.68</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="46">
         <v>2.41</v>
       </c>
       <c r="Q5" s="52">
         <v>-1.4</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="40">
         <v>-4.81</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="43">
         <v>-2.27</v>
       </c>
-      <c r="T5" s="40">
-        <v>-7.02</v>
+      <c r="T5" s="44">
+        <v>-7.55</v>
       </c>
     </row>
     <row r="6">
@@ -2594,7 +2642,7 @@
       <c r="C6" t="str">
         <v>002716</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="53" t="str">
         <v>净买: 1382.25万</v>
       </c>
       <c r="E6">
@@ -2609,41 +2657,41 @@
       <c r="H6">
         <v>-10</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="61">
         <v>2.54</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="56">
         <v>4.29</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="54">
         <v>1.59</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="55">
         <v>2.22</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="64">
         <v>-0.79</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="65">
         <v>2.86</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="57">
         <v>1.11</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="58">
         <v>2.06</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="59">
         <v>0.79</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="60">
         <v>-2.7</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="62">
         <v>-2.22</v>
       </c>
-      <c r="T6" s="61">
-        <v>95.87</v>
+      <c r="T6" s="63">
+        <v>83.65</v>
       </c>
     </row>
     <row r="7">
@@ -2656,7 +2704,7 @@
       <c r="C7" t="str">
         <v>600179</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="76" t="str">
         <v>净卖: -4985.00万</v>
       </c>
       <c r="E7">
@@ -2671,41 +2719,41 @@
       <c r="H7">
         <v>10.07</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="71">
         <v>0</v>
       </c>
       <c r="J7" s="66">
         <v>9.96</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="72">
         <v>20.93</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="67">
         <v>33.13</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="68">
         <v>19.92</v>
       </c>
-      <c r="N7" s="68">
+      <c r="N7" s="69">
         <v>11.59</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="73">
         <v>12.2</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="77">
         <v>5.69</v>
       </c>
-      <c r="Q7" s="76">
+      <c r="Q7" s="70">
         <v>6.3</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="74">
         <v>6.3</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="78">
         <v>4.07</v>
       </c>
-      <c r="T7" s="78">
-        <v>-7.72</v>
+      <c r="T7" s="75">
+        <v>-11.79</v>
       </c>
     </row>
     <row r="8">
@@ -2718,7 +2766,7 @@
       <c r="C8" t="str">
         <v>603138</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="87" t="str">
         <v>净卖: -1937.66万</v>
       </c>
       <c r="E8">
@@ -2739,35 +2787,35 @@
       <c r="J8" s="79">
         <v>2.79</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="84">
         <v>-7.47</v>
       </c>
-      <c r="L8" s="90">
+      <c r="L8" s="88">
         <v>-1.28</v>
       </c>
-      <c r="M8" s="80">
+      <c r="M8" s="89">
         <v>-1.59</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="80">
         <v>0.8</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="85">
         <v>-1.41</v>
       </c>
-      <c r="P8" s="82">
+      <c r="P8" s="81">
         <v>-8.58</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="90">
         <v>-10.21</v>
       </c>
-      <c r="R8" s="91">
+      <c r="R8" s="82">
         <v>-6.28</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="91">
         <v>-6.41</v>
       </c>
-      <c r="T8" s="88">
-        <v>-13.35</v>
+      <c r="T8" s="86">
+        <v>-13.93</v>
       </c>
     </row>
     <row r="9">
@@ -2780,7 +2828,7 @@
       <c r="C9" t="str">
         <v>605162</v>
       </c>
-      <c r="D9" s="98" t="str">
+      <c r="D9" s="93" t="str">
         <v>净卖: -614.82万</v>
       </c>
       <c r="E9">
@@ -2795,29 +2843,35 @@
       <c r="H9">
         <v>-5.12</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="94">
         <v>-3.83</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="95">
         <v>-2.18</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="99">
         <v>-4.43</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="96">
         <v>5.1</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="100">
         <v>3.98</v>
       </c>
-      <c r="N9" t="str"/>
-      <c r="O9" t="str"/>
-      <c r="P9" t="str"/>
+      <c r="N9" s="98">
+        <v>1.35</v>
+      </c>
+      <c r="O9" s="101">
+        <v>-2.03</v>
+      </c>
+      <c r="P9" s="97">
+        <v>-9.98</v>
+      </c>
       <c r="Q9" t="str"/>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="97">
-        <v>3.98</v>
+      <c r="T9" s="92">
+        <v>-9.98</v>
       </c>
     </row>
     <row r="10">
@@ -2847,13 +2901,13 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>7</v>
@@ -2879,41 +2933,41 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="101">
+      <c r="I11" s="109">
         <v>50</v>
       </c>
-      <c r="J11" s="107">
+      <c r="J11" s="106">
         <v>87.5</v>
       </c>
-      <c r="K11" s="104">
+      <c r="K11" s="110">
         <v>75</v>
       </c>
-      <c r="L11" s="109">
+      <c r="L11" s="113">
         <v>87.5</v>
       </c>
-      <c r="M11" s="105">
+      <c r="M11" s="107">
         <v>75</v>
       </c>
-      <c r="N11" s="106">
+      <c r="N11" s="102">
         <v>100</v>
       </c>
-      <c r="O11" s="110">
-        <v>85.71</v>
-      </c>
-      <c r="P11" s="99">
-        <v>71.43</v>
-      </c>
-      <c r="Q11" s="100">
+      <c r="O11" s="105">
+        <v>75</v>
+      </c>
+      <c r="P11" s="103">
+        <v>62.5</v>
+      </c>
+      <c r="Q11" s="111">
         <v>57.14</v>
       </c>
-      <c r="R11" s="102">
+      <c r="R11" s="112">
         <v>42.86</v>
       </c>
-      <c r="S11" s="103">
+      <c r="S11" s="104">
         <v>42.86</v>
       </c>
       <c r="T11" s="108">
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -2927,41 +2981,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="111">
+      <c r="I12" s="118">
         <v>3.52</v>
       </c>
-      <c r="J12" s="116">
+      <c r="J12" s="119">
         <v>8.41</v>
       </c>
-      <c r="K12" s="117">
+      <c r="K12" s="124">
         <v>7.52</v>
       </c>
-      <c r="L12" s="121">
+      <c r="L12" s="120">
         <v>12.33</v>
       </c>
-      <c r="M12" s="112">
+      <c r="M12" s="125">
         <v>11.1</v>
       </c>
-      <c r="N12" s="114">
-        <v>10.93</v>
-      </c>
-      <c r="O12" s="118">
-        <v>10.13</v>
-      </c>
-      <c r="P12" s="115">
-        <v>8.54</v>
-      </c>
-      <c r="Q12" s="113">
+      <c r="N12" s="115">
+        <v>9.73</v>
+      </c>
+      <c r="O12" s="116">
+        <v>8.61</v>
+      </c>
+      <c r="P12" s="121">
+        <v>6.23</v>
+      </c>
+      <c r="Q12" s="122">
         <v>7.15</v>
       </c>
-      <c r="R12" s="119">
+      <c r="R12" s="123">
         <v>7.18</v>
       </c>
-      <c r="S12" s="120">
+      <c r="S12" s="114">
         <v>10.53</v>
       </c>
-      <c r="T12" s="122">
-        <v>19.78</v>
+      <c r="T12" s="117">
+        <v>15.91</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/招商深南东/index.xlsx
+++ b/youzi/招商深南东/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="127">
+  <fills count="128">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,7 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,13 +117,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,49 +267,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,115 +399,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -255,25 +495,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,175 +579,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -465,67 +669,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
+        <fgColor rgb="FF65C07A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -537,138 +681,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -687,25 +699,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -757,38 +793,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="126">
+  <borders count="127">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1675,7 +1688,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -2050,6 +2063,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="125" fillId="126" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="126" fillId="127" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -2394,7 +2410,7 @@
       <c r="C2" t="str">
         <v>601015</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="8" t="str">
         <v>净卖: -308.44万</v>
       </c>
       <c r="E2">
@@ -2409,41 +2425,41 @@
       <c r="H2">
         <v>-0.32</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>10.51</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="9">
         <v>13.38</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="11">
         <v>7.64</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="3">
         <v>10.19</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="12">
         <v>8.6</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="13">
         <v>6.69</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="1">
         <v>1.91</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="4">
         <v>-1.91</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="5">
         <v>-0.96</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="6">
         <v>-0.96</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="10">
         <v>-0.64</v>
       </c>
-      <c r="T2" s="13">
-        <v>26.75</v>
+      <c r="T2" s="7">
+        <v>27.39</v>
       </c>
     </row>
     <row r="3">
@@ -2456,7 +2472,7 @@
       <c r="C3" t="str">
         <v>301617</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 2288.65万</v>
       </c>
       <c r="E3">
@@ -2471,41 +2487,41 @@
       <c r="H3">
         <v>2.21</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="19">
         <v>6.26</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="26">
         <v>16.21</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="20">
         <v>17.8</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="21">
         <v>30.66</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="22">
         <v>36.79</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="23">
         <v>36.59</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="24">
         <v>44.45</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="17">
         <v>45.34</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="14">
         <v>40.3</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="15">
         <v>32.27</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="16">
         <v>49.92</v>
       </c>
-      <c r="T3" s="23">
-        <v>34.85</v>
+      <c r="T3" s="18">
+        <v>32.93</v>
       </c>
     </row>
     <row r="4">
@@ -2518,7 +2534,7 @@
       <c r="C4" t="str">
         <v>001332</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -1202.20万</v>
       </c>
       <c r="E4">
@@ -2533,41 +2549,41 @@
       <c r="H4">
         <v>-1</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="39">
         <v>-1.69</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="30">
         <v>4.19</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="31">
         <v>7</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="32">
         <v>7.3</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="27">
         <v>12.09</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="35">
         <v>13.36</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="33">
         <v>8.95</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="28">
         <v>14.78</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="36">
         <v>15.24</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="37">
         <v>26.45</v>
       </c>
       <c r="S4" s="34">
         <v>31.23</v>
       </c>
-      <c r="T4" s="35">
-        <v>25.29</v>
+      <c r="T4" s="29">
+        <v>37.82</v>
       </c>
     </row>
     <row r="5">
@@ -2580,7 +2596,7 @@
       <c r="C5" t="str">
         <v>002674</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="52" t="str">
         <v>净卖: -488.16万</v>
       </c>
       <c r="E5">
@@ -2595,16 +2611,16 @@
       <c r="H5">
         <v>-3.79</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="49">
         <v>14.37</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="40">
         <v>18.65</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="41">
         <v>17.11</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="46">
         <v>11.3</v>
       </c>
       <c r="M5" s="45">
@@ -2613,23 +2629,23 @@
       <c r="N5" s="42">
         <v>4.61</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="50">
         <v>3.68</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="43">
         <v>2.41</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="47">
         <v>-1.4</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="51">
         <v>-4.81</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="44">
         <v>-2.27</v>
       </c>
-      <c r="T5" s="44">
-        <v>-7.55</v>
+      <c r="T5" s="48">
+        <v>-6.48</v>
       </c>
     </row>
     <row r="6">
@@ -2642,7 +2658,7 @@
       <c r="C6" t="str">
         <v>002716</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="60" t="str">
         <v>净买: 1382.25万</v>
       </c>
       <c r="E6">
@@ -2657,41 +2673,41 @@
       <c r="H6">
         <v>-10</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="63">
         <v>2.54</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="64">
         <v>4.29</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="65">
         <v>1.59</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="53">
         <v>2.22</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="61">
         <v>-0.79</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="54">
         <v>2.86</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="55">
         <v>1.11</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="56">
         <v>2.06</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="57">
         <v>0.79</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="58">
         <v>-2.7</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="59">
         <v>-2.22</v>
       </c>
-      <c r="T6" s="63">
-        <v>83.65</v>
+      <c r="T6" s="62">
+        <v>80.95</v>
       </c>
     </row>
     <row r="7">
@@ -2719,41 +2735,41 @@
       <c r="H7">
         <v>10.07</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="68">
         <v>0</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="74">
         <v>9.96</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="69">
         <v>20.93</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="77">
         <v>33.13</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="70">
         <v>19.92</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="71">
         <v>11.59</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="72">
         <v>12.2</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="75">
         <v>5.69</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="78">
         <v>6.3</v>
       </c>
-      <c r="R7" s="74">
+      <c r="R7" s="66">
         <v>6.3</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="67">
         <v>4.07</v>
       </c>
-      <c r="T7" s="75">
-        <v>-11.79</v>
+      <c r="T7" s="73">
+        <v>-13.41</v>
       </c>
     </row>
     <row r="8">
@@ -2766,7 +2782,7 @@
       <c r="C8" t="str">
         <v>603138</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="90" t="str">
         <v>净卖: -1937.66万</v>
       </c>
       <c r="E8">
@@ -2781,41 +2797,41 @@
       <c r="H8">
         <v>10.02</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="81">
         <v>0</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="86">
         <v>2.79</v>
       </c>
-      <c r="K8" s="84">
+      <c r="K8" s="91">
         <v>-7.47</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="79">
         <v>-1.28</v>
       </c>
       <c r="M8" s="89">
         <v>-1.59</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="82">
         <v>0.8</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="80">
         <v>-1.41</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="83">
         <v>-8.58</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="87">
         <v>-10.21</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="84">
         <v>-6.28</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="85">
         <v>-6.41</v>
       </c>
-      <c r="T8" s="86">
-        <v>-13.93</v>
+      <c r="T8" s="88">
+        <v>-16.09</v>
       </c>
     </row>
     <row r="9">
@@ -2828,7 +2844,7 @@
       <c r="C9" t="str">
         <v>605162</v>
       </c>
-      <c r="D9" s="93" t="str">
+      <c r="D9" s="92" t="str">
         <v>净卖: -614.82万</v>
       </c>
       <c r="E9">
@@ -2843,35 +2859,37 @@
       <c r="H9">
         <v>-5.12</v>
       </c>
-      <c r="I9" s="94">
+      <c r="I9" s="102">
         <v>-3.83</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="101">
         <v>-2.18</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="93">
         <v>-4.43</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="94">
         <v>5.1</v>
       </c>
-      <c r="M9" s="100">
+      <c r="M9" s="95">
         <v>3.98</v>
       </c>
       <c r="N9" s="98">
         <v>1.35</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="96">
         <v>-2.03</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="99">
         <v>-9.98</v>
       </c>
-      <c r="Q9" t="str"/>
+      <c r="Q9" s="100">
+        <v>-10.5</v>
+      </c>
       <c r="R9" t="str"/>
       <c r="S9" t="str"/>
-      <c r="T9" s="92">
-        <v>-9.98</v>
+      <c r="T9" s="97">
+        <v>-10.5</v>
       </c>
     </row>
     <row r="10">
@@ -2910,7 +2928,7 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>7</v>
@@ -2933,40 +2951,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="109">
+      <c r="I11" s="107">
         <v>50</v>
       </c>
-      <c r="J11" s="106">
+      <c r="J11" s="108">
         <v>87.5</v>
       </c>
-      <c r="K11" s="110">
+      <c r="K11" s="111">
         <v>75</v>
       </c>
-      <c r="L11" s="113">
+      <c r="L11" s="112">
         <v>87.5</v>
       </c>
-      <c r="M11" s="107">
+      <c r="M11" s="114">
         <v>75</v>
       </c>
-      <c r="N11" s="102">
+      <c r="N11" s="109">
         <v>100</v>
       </c>
-      <c r="O11" s="105">
+      <c r="O11" s="113">
         <v>75</v>
       </c>
-      <c r="P11" s="103">
+      <c r="P11" s="104">
         <v>62.5</v>
       </c>
-      <c r="Q11" s="111">
-        <v>57.14</v>
-      </c>
-      <c r="R11" s="112">
+      <c r="Q11" s="105">
+        <v>50</v>
+      </c>
+      <c r="R11" s="103">
         <v>42.86</v>
       </c>
-      <c r="S11" s="104">
+      <c r="S11" s="106">
         <v>42.86</v>
       </c>
-      <c r="T11" s="108">
+      <c r="T11" s="110">
         <v>50</v>
       </c>
     </row>
@@ -2981,41 +2999,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="118">
+      <c r="I12" s="124">
         <v>3.52</v>
       </c>
-      <c r="J12" s="119">
+      <c r="J12" s="115">
         <v>8.41</v>
       </c>
-      <c r="K12" s="124">
+      <c r="K12" s="120">
         <v>7.52</v>
       </c>
-      <c r="L12" s="120">
+      <c r="L12" s="116">
         <v>12.33</v>
       </c>
-      <c r="M12" s="125">
+      <c r="M12" s="117">
         <v>11.1</v>
       </c>
-      <c r="N12" s="115">
+      <c r="N12" s="121">
         <v>9.73</v>
       </c>
-      <c r="O12" s="116">
+      <c r="O12" s="125">
         <v>8.61</v>
       </c>
-      <c r="P12" s="121">
+      <c r="P12" s="122">
         <v>6.23</v>
       </c>
-      <c r="Q12" s="122">
-        <v>7.15</v>
-      </c>
-      <c r="R12" s="123">
+      <c r="Q12" s="123">
+        <v>4.94</v>
+      </c>
+      <c r="R12" s="118">
         <v>7.18</v>
       </c>
-      <c r="S12" s="114">
+      <c r="S12" s="119">
         <v>10.53</v>
       </c>
-      <c r="T12" s="117">
-        <v>15.91</v>
+      <c r="T12" s="126">
+        <v>16.58</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/招商深南东/index.xlsx
+++ b/youzi/招商深南东/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="128">
+  <fills count="129">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,24 +39,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF1B1B7"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFACDDB7"/>
         <bgColor/>
       </patternFill>
@@ -69,7 +87,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
+        <fgColor rgb="FFE3F3E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,91 +213,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2E6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4453"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,73 +387,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA5AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -267,49 +441,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4453"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,121 +579,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFA5AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ABB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED98A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,73 +669,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2E6CA"/>
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -525,139 +705,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -669,90 +723,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -793,8 +763,51 @@
         <bgColor/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="127">
+  <borders count="128">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1688,7 +1701,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -2066,6 +2079,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="126" fillId="127" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="127" fillId="128" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -2410,7 +2426,7 @@
       <c r="C2" t="str">
         <v>601015</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -308.44万</v>
       </c>
       <c r="E2">
@@ -2425,41 +2441,41 @@
       <c r="H2">
         <v>-0.32</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="13">
         <v>10.51</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="4">
         <v>13.38</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="1">
         <v>7.64</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="10">
         <v>10.19</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="11">
         <v>8.6</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="5">
         <v>6.69</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="6">
         <v>1.91</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="7">
         <v>-1.91</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="2">
         <v>-0.96</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="8">
         <v>-0.96</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="9">
         <v>-0.64</v>
       </c>
-      <c r="T2" s="7">
-        <v>27.39</v>
+      <c r="T2" s="12">
+        <v>28.34</v>
       </c>
     </row>
     <row r="3">
@@ -2472,7 +2488,7 @@
       <c r="C3" t="str">
         <v>301617</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="26" t="str">
         <v>净买: 2288.65万</v>
       </c>
       <c r="E3">
@@ -2487,41 +2503,41 @@
       <c r="H3">
         <v>2.21</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="14">
         <v>6.26</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="15">
         <v>16.21</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="23">
         <v>17.8</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="16">
         <v>30.66</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="19">
         <v>36.79</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="17">
         <v>36.59</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="20">
         <v>44.45</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="18">
         <v>45.34</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="21">
         <v>40.3</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="22">
         <v>32.27</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="24">
         <v>49.92</v>
       </c>
-      <c r="T3" s="18">
-        <v>32.93</v>
+      <c r="T3" s="25">
+        <v>28.78</v>
       </c>
     </row>
     <row r="4">
@@ -2534,7 +2550,7 @@
       <c r="C4" t="str">
         <v>001332</v>
       </c>
-      <c r="D4" s="38" t="str">
+      <c r="D4" s="29" t="str">
         <v>净卖: -1202.20万</v>
       </c>
       <c r="E4">
@@ -2549,41 +2565,41 @@
       <c r="H4">
         <v>-1</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="32">
         <v>-1.69</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="33">
         <v>4.19</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="34">
         <v>7</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="30">
         <v>7.3</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="36">
         <v>12.09</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="31">
         <v>13.36</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="37">
         <v>8.95</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="39">
         <v>14.78</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="38">
         <v>15.24</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="27">
         <v>26.45</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="35">
         <v>31.23</v>
       </c>
-      <c r="T4" s="29">
-        <v>37.82</v>
+      <c r="T4" s="28">
+        <v>41.04</v>
       </c>
     </row>
     <row r="5">
@@ -2596,7 +2612,7 @@
       <c r="C5" t="str">
         <v>002674</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="43" t="str">
         <v>净卖: -488.16万</v>
       </c>
       <c r="E5">
@@ -2614,38 +2630,38 @@
       <c r="I5" s="49">
         <v>14.37</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="50">
         <v>18.65</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="46">
         <v>17.11</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="51">
         <v>11.3</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="52">
         <v>9.76</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="44">
         <v>4.61</v>
       </c>
-      <c r="O5" s="50">
+      <c r="O5" s="40">
         <v>3.68</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="47">
         <v>2.41</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="41">
         <v>-1.4</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="45">
         <v>-4.81</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="42">
         <v>-2.27</v>
       </c>
       <c r="T5" s="48">
-        <v>-6.48</v>
+        <v>-10.96</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2674,7 @@
       <c r="C6" t="str">
         <v>002716</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="58" t="str">
         <v>净买: 1382.25万</v>
       </c>
       <c r="E6">
@@ -2676,38 +2692,38 @@
       <c r="I6" s="63">
         <v>2.54</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="59">
         <v>4.29</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="60">
         <v>1.59</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="65">
         <v>2.22</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="53">
         <v>-0.79</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="61">
         <v>2.86</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="54">
         <v>1.11</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="55">
         <v>2.06</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="62">
         <v>0.79</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="64">
         <v>-2.7</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="56">
         <v>-2.22</v>
       </c>
-      <c r="T6" s="62">
-        <v>80.95</v>
+      <c r="T6" s="57">
+        <v>74.76</v>
       </c>
     </row>
     <row r="7">
@@ -2720,7 +2736,7 @@
       <c r="C7" t="str">
         <v>600179</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -4985.00万</v>
       </c>
       <c r="E7">
@@ -2738,37 +2754,37 @@
       <c r="I7" s="68">
         <v>0</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="73">
         <v>9.96</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="74">
         <v>20.93</v>
       </c>
-      <c r="L7" s="77">
+      <c r="L7" s="75">
         <v>33.13</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="78">
         <v>19.92</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="69">
         <v>11.59</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="76">
         <v>12.2</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="66">
         <v>5.69</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="70">
         <v>6.3</v>
       </c>
-      <c r="R7" s="66">
+      <c r="R7" s="71">
         <v>6.3</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="77">
         <v>4.07</v>
       </c>
-      <c r="T7" s="73">
+      <c r="T7" s="72">
         <v>-13.41</v>
       </c>
     </row>
@@ -2782,7 +2798,7 @@
       <c r="C8" t="str">
         <v>603138</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="91" t="str">
         <v>净卖: -1937.66万</v>
       </c>
       <c r="E8">
@@ -2797,41 +2813,41 @@
       <c r="H8">
         <v>10.02</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="79">
         <v>0</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="88">
         <v>2.79</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="87">
         <v>-7.47</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="83">
         <v>-1.28</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="84">
         <v>-1.59</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="89">
         <v>0.8</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="90">
         <v>-1.41</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="80">
         <v>-8.58</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="81">
         <v>-10.21</v>
       </c>
-      <c r="R8" s="84">
+      <c r="R8" s="85">
         <v>-6.28</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="82">
         <v>-6.41</v>
       </c>
-      <c r="T8" s="88">
-        <v>-16.09</v>
+      <c r="T8" s="86">
+        <v>-16.67</v>
       </c>
     </row>
     <row r="9">
@@ -2844,7 +2860,7 @@
       <c r="C9" t="str">
         <v>605162</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="100" t="str">
         <v>净卖: -614.82万</v>
       </c>
       <c r="E9">
@@ -2859,37 +2875,39 @@
       <c r="H9">
         <v>-5.12</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="101">
         <v>-3.83</v>
       </c>
-      <c r="J9" s="101">
+      <c r="J9" s="97">
         <v>-2.18</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="102">
         <v>-4.43</v>
       </c>
       <c r="L9" s="94">
         <v>5.1</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="98">
         <v>3.98</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="103">
         <v>1.35</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="92">
         <v>-2.03</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="93">
         <v>-9.98</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="95">
         <v>-10.5</v>
       </c>
-      <c r="R9" t="str"/>
+      <c r="R9" s="96">
+        <v>-13.58</v>
+      </c>
       <c r="S9" t="str"/>
-      <c r="T9" s="97">
-        <v>-10.5</v>
+      <c r="T9" s="99">
+        <v>-13.58</v>
       </c>
     </row>
     <row r="10">
@@ -2931,7 +2949,7 @@
         <v>8</v>
       </c>
       <c r="R10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>7</v>
@@ -2951,40 +2969,40 @@
       <c r="F11" t="str"/>
       <c r="G11" t="str"/>
       <c r="H11" t="str"/>
-      <c r="I11" s="107">
+      <c r="I11" s="111">
         <v>50</v>
       </c>
-      <c r="J11" s="108">
+      <c r="J11" s="112">
         <v>87.5</v>
       </c>
-      <c r="K11" s="111">
+      <c r="K11" s="104">
         <v>75</v>
       </c>
-      <c r="L11" s="112">
+      <c r="L11" s="113">
         <v>87.5</v>
       </c>
-      <c r="M11" s="114">
+      <c r="M11" s="107">
         <v>75</v>
       </c>
-      <c r="N11" s="109">
+      <c r="N11" s="115">
         <v>100</v>
       </c>
-      <c r="O11" s="113">
+      <c r="O11" s="108">
         <v>75</v>
       </c>
-      <c r="P11" s="104">
+      <c r="P11" s="109">
         <v>62.5</v>
       </c>
       <c r="Q11" s="105">
         <v>50</v>
       </c>
-      <c r="R11" s="103">
-        <v>42.86</v>
+      <c r="R11" s="110">
+        <v>37.5</v>
       </c>
       <c r="S11" s="106">
         <v>42.86</v>
       </c>
-      <c r="T11" s="110">
+      <c r="T11" s="114">
         <v>50</v>
       </c>
     </row>
@@ -2999,41 +3017,41 @@
       <c r="F12" t="str"/>
       <c r="G12" t="str"/>
       <c r="H12" t="str"/>
-      <c r="I12" s="124">
+      <c r="I12" s="119">
         <v>3.52</v>
       </c>
-      <c r="J12" s="115">
+      <c r="J12" s="124">
         <v>8.41</v>
       </c>
-      <c r="K12" s="120">
+      <c r="K12" s="125">
         <v>7.52</v>
       </c>
-      <c r="L12" s="116">
+      <c r="L12" s="123">
         <v>12.33</v>
       </c>
-      <c r="M12" s="117">
+      <c r="M12" s="126">
         <v>11.1</v>
       </c>
-      <c r="N12" s="121">
+      <c r="N12" s="127">
         <v>9.73</v>
       </c>
-      <c r="O12" s="125">
+      <c r="O12" s="116">
         <v>8.61</v>
       </c>
-      <c r="P12" s="122">
+      <c r="P12" s="117">
         <v>6.23</v>
       </c>
-      <c r="Q12" s="123">
+      <c r="Q12" s="120">
         <v>4.94</v>
       </c>
       <c r="R12" s="118">
-        <v>7.18</v>
-      </c>
-      <c r="S12" s="119">
+        <v>4.59</v>
+      </c>
+      <c r="S12" s="121">
         <v>10.53</v>
       </c>
-      <c r="T12" s="126">
-        <v>16.58</v>
+      <c r="T12" s="122">
+        <v>14.79</v>
       </c>
     </row>
   </sheetData>
